--- a/PROYECTOS/MEZANINE MA/Lista de materiales.xlsx
+++ b/PROYECTOS/MEZANINE MA/Lista de materiales.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30213"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIC\Downloads\CURSO SKETCHUP\PROYECTOS\MEZANINE MA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D584E346-908B-45DC-AE1B-F49856D90098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D808547B-6AD1-478E-84E3-4A48EC1CA670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9C38CAA7-9F0A-40CC-8992-24B3D9ED1EBA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9C38CAA7-9F0A-40CC-8992-24B3D9ED1EBA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
+    <sheet name="Precio Melamina Trupan" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="176">
   <si>
     <t>LISTA DE MATERIALES</t>
   </si>
@@ -154,6 +156,421 @@
   </si>
   <si>
     <t>Herramientas</t>
+  </si>
+  <si>
+    <t>MAD CENTER</t>
+  </si>
+  <si>
+    <t>Servicio Tapacanto</t>
+  </si>
+  <si>
+    <t>Servicio corte 45</t>
+  </si>
+  <si>
+    <t>Servicio perforacion</t>
+  </si>
+  <si>
+    <t>BERNEK
+69707359 Ventas
+69745353 Tecnico (Luis)</t>
+  </si>
+  <si>
+    <t>Otras considereciones</t>
+  </si>
+  <si>
+    <t>5mm Reborde
+5mm Grosor cierra</t>
+  </si>
+  <si>
+    <t>Melamina Tipo Quarzo 18mm</t>
+  </si>
+  <si>
+    <t>Melamina Normal 15mm</t>
+  </si>
+  <si>
+    <t>Melamina Normal 18mm</t>
+  </si>
+  <si>
+    <t>MOYATEC
+57053550 Ventas</t>
+  </si>
+  <si>
+    <t>PLACA CENTRO
+76538609 Ventas
+69713720 Ferreteria</t>
+  </si>
+  <si>
+    <t>720 (275x185)</t>
+  </si>
+  <si>
+    <t>700 (260x183)</t>
+  </si>
+  <si>
+    <t>Tipos de trabajo</t>
+  </si>
+  <si>
+    <t>Realizan cortes rectos y L.</t>
+  </si>
+  <si>
+    <t>Realizan cortes rectos</t>
+  </si>
+  <si>
+    <t>Realizan cortes rectos, cortes 45, perforaciones bisagras, perfilados,
+cortes en L, ranurados.</t>
+  </si>
+  <si>
+    <t>Realizan cortes rectos, perfilados</t>
+  </si>
+  <si>
+    <t>Servicio Tapacanto manual</t>
+  </si>
+  <si>
+    <t>Servicio enchapado doble</t>
+  </si>
+  <si>
+    <t>6.50-7</t>
+  </si>
+  <si>
+    <t>2.8 (4mmx22mm)
+3 (6mmx22mm)</t>
+  </si>
+  <si>
+    <t>2.8
+3.5</t>
+  </si>
+  <si>
+    <t>SCHWARTZ VRENA
+62130000 Ventas</t>
+  </si>
+  <si>
+    <t>721 (Texturizado)
+793 (Synchro)</t>
+  </si>
+  <si>
+    <t>590 (260x183)
+560 (260x183) Blanco Bernek</t>
+  </si>
+  <si>
+    <t>Melamina</t>
+  </si>
+  <si>
+    <t>Nivel láser (muy recomendable para instalaciones)</t>
+  </si>
+  <si>
+    <t>Medición y marcado</t>
+  </si>
+  <si>
+    <t>Guías y plantillas</t>
+  </si>
+  <si>
+    <t>Perforación</t>
+  </si>
+  <si>
+    <t>2 prensas tipo F</t>
+  </si>
+  <si>
+    <t>Ensamblado</t>
+  </si>
+  <si>
+    <t>Prensas</t>
+  </si>
+  <si>
+    <t>Cortes perfectos</t>
+  </si>
+  <si>
+    <t>Sierra circular</t>
+  </si>
+  <si>
+    <t>Disco especial para melamina (60–80 dientes)</t>
+  </si>
+  <si>
+    <t>Riel guía para la sierra</t>
+  </si>
+  <si>
+    <t>Banco de corte</t>
+  </si>
+  <si>
+    <t>Aspiradora para polvo</t>
+  </si>
+  <si>
+    <t>Acabado tapacantos</t>
+  </si>
+  <si>
+    <t>Accesorios alineacion</t>
+  </si>
+  <si>
+    <t>Consumibles</t>
+  </si>
+  <si>
+    <t>4 prensas rápidas de 60 cm</t>
+  </si>
+  <si>
+    <t>2 Prensas tipo C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Prensas de esquina de 90° </t>
+  </si>
+  <si>
+    <t>1 Broca Forstner de 35 mm (para bisagras cazoleta Nro 26/2.6 cm)</t>
+  </si>
+  <si>
+    <t>1 Cinta métrica de buena calidad (5 m o 8 m)</t>
+  </si>
+  <si>
+    <t>1 Regla metálica de 60 cm o 1 m</t>
+  </si>
+  <si>
+    <t>1 Nivel de burbuja (60 cm)</t>
+  </si>
+  <si>
+    <t>1 Lápiz de carpintero o portaminas de punta fina</t>
+  </si>
+  <si>
+    <t>1 Gramil carpintero</t>
+  </si>
+  <si>
+    <t>1 Tijera</t>
+  </si>
+  <si>
+    <t>1 Estilete</t>
+  </si>
+  <si>
+    <t>1 Formon</t>
+  </si>
+  <si>
+    <t>1 Taladro + Atornillador inalámbrico</t>
+  </si>
+  <si>
+    <t>1 kit atornillador con accesorios</t>
+  </si>
+  <si>
+    <t>1 Juego de brocas para madera (3mm requerido)</t>
+  </si>
+  <si>
+    <t>1 Brocas Brad Point (de punta centradora)</t>
+  </si>
+  <si>
+    <t>1 Plantilla para bisagras de 35 mm</t>
+  </si>
+  <si>
+    <t>1 Plantilla para perforaciones tipo Confirmat</t>
+  </si>
+  <si>
+    <t>1 Plantilla para minifix</t>
+  </si>
+  <si>
+    <t>1 Plantilla para tarugos</t>
+  </si>
+  <si>
+    <t>1 Guía para instalar correderas</t>
+  </si>
+  <si>
+    <t>1 Plantilla para tiradores</t>
+  </si>
+  <si>
+    <t>1 Correas de apriete para muebles grandes</t>
+  </si>
+  <si>
+    <t>1 Martillo de goma blanca</t>
+  </si>
+  <si>
+    <t>1 Destornillador Manual + accesorios</t>
+  </si>
+  <si>
+    <t>1 Juego de puntas PH, PZ y Torx (Punta estrella, punta cruz, 6 puntas)</t>
+  </si>
+  <si>
+    <t>1 Kit llaves Allen</t>
+  </si>
+  <si>
+    <t>1 Llave de matraca pequeña (para espacios espacios pequeños)</t>
+  </si>
+  <si>
+    <t>1 Plancha para canto (si usas canto termofusible)</t>
+  </si>
+  <si>
+    <t>1 Cortador de canto</t>
+  </si>
+  <si>
+    <t>1 Lima fina</t>
+  </si>
+  <si>
+    <t>1 Taco de canto</t>
+  </si>
+  <si>
+    <t>1 Rodillo para presionar el canto</t>
+  </si>
+  <si>
+    <t>1 Kit cuñas plásticas</t>
+  </si>
+  <si>
+    <t>1 Kit separadores de 2 /3/4 mm</t>
+  </si>
+  <si>
+    <t>1 Bloques de referencia</t>
+  </si>
+  <si>
+    <t>1 Kit Calzas niveladoras</t>
+  </si>
+  <si>
+    <t>1 Kit topes de montaje</t>
+  </si>
+  <si>
+    <t>1 Cola PVA para madera 600ml (clefa)</t>
+  </si>
+  <si>
+    <t>1 Cinta de enmascarar (cinta masquin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Alcohol isopropílico 1lt </t>
+  </si>
+  <si>
+    <t>1 Paño de microfibra</t>
+  </si>
+  <si>
+    <t>1 Lubricante seco de silicona (auto)</t>
+  </si>
+  <si>
+    <t>1 Kit marcadores reparadores de melamina</t>
+  </si>
+  <si>
+    <t>1 Lija de agua nro 150</t>
+  </si>
+  <si>
+    <t>1 bolsa de Palitos de helado</t>
+  </si>
+  <si>
+    <t>100 Tornillos 3.5x50mm (melamina 15mm, union por lados )</t>
+  </si>
+  <si>
+    <t>100 Tornillos 3.5x25mm (melamina 15mm, union por cara)</t>
+  </si>
+  <si>
+    <t>100 Tornillos 3.5x15mm (melamina 15mm, bisagras y correderas)</t>
+  </si>
+  <si>
+    <t>100 Tornillos 4.0x50mm (melamina 15mm)</t>
+  </si>
+  <si>
+    <t>100 Tornillos 4.0x25mm (melamina 15mm)</t>
+  </si>
+  <si>
+    <t>609(275x185)</t>
+  </si>
+  <si>
+    <t>810(275x185)</t>
+  </si>
+  <si>
+    <t>719(275x186)</t>
+  </si>
+  <si>
+    <t>365 (marca Total 8v)</t>
+  </si>
+  <si>
+    <t>GAMELI (Internet)
+69705967 Ventas</t>
+  </si>
+  <si>
+    <t>1 Alicate tapa tornillo 8mm (compatible para 3.5 y 4 mm)</t>
+  </si>
+  <si>
+    <t>1 Avellanador con tope</t>
+  </si>
+  <si>
+    <t>30 (10 brocas)</t>
+  </si>
+  <si>
+    <t>115 (un par)</t>
+  </si>
+  <si>
+    <t>1 par de abrazaderas de fijacion de cajon</t>
+  </si>
+  <si>
+    <t>295 (un par)</t>
+  </si>
+  <si>
+    <t>1 par de sujetador para frente de cajon</t>
+  </si>
+  <si>
+    <t>235 (un par)</t>
+  </si>
+  <si>
+    <t>Preguntar cual me sirve</t>
+  </si>
+  <si>
+    <t>75 y 80 (modelo abierto y cerrado)</t>
+  </si>
+  <si>
+    <t>Preguntar si el lo mismo que presen esquina</t>
+  </si>
+  <si>
+    <t>1 Kit de Plantilla para rieles de cajon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perguntar hay dos precios 115 y 130 </t>
+  </si>
+  <si>
+    <t>1 Kit de plantilla para montaje de puertas de armario</t>
+  </si>
+  <si>
+    <t>135, 160 Opcional, cual es mejor.
+El de 490 ya contiene todo lo anterior</t>
+  </si>
+  <si>
+    <t>1 Guía para perforar a 30/45/90° (tipo kreg)</t>
+  </si>
+  <si>
+    <t>Perfora a 15grados. 
+Se usan tornillos comunes?
+Cuales es mejor el de 390 o 120</t>
+  </si>
+  <si>
+    <t>1 Broca escalonada de 95mm (para agujeros ocultos)</t>
+  </si>
+  <si>
+    <t>100 Tornillos 8.0x3.0x25 para agujeros ocultos (sistema kreg)</t>
+  </si>
+  <si>
+    <t>1 Guia de bisagra congrejo, cazoleta</t>
+  </si>
+  <si>
+    <t>1  Regla escuadra en T de angulo ajustable (recomendado)</t>
+  </si>
+  <si>
+    <t>Recomendado</t>
+  </si>
+  <si>
+    <t>1 Escuadra de carpintero con nivel de burbuja de 7 pulgadas</t>
+  </si>
+  <si>
+    <t>1 tope de profundidad para broca</t>
+  </si>
+  <si>
+    <t>1 Extension felxible de 30 cm (chicotillo curvo)</t>
+  </si>
+  <si>
+    <t>5 Marcador carpintero (negro, rojo, azul, verde, blanco)</t>
+  </si>
+  <si>
+    <t>Fluroecente y doble cara</t>
+  </si>
+  <si>
+    <t>1 Punzon automatico (Marcador de agujeros)</t>
+  </si>
+  <si>
+    <t>1 Pulsera magnetica de tornillos (recomendado)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Tapa fondo</t>
+  </si>
+  <si>
+    <t>240 (275x185x3)</t>
+  </si>
+  <si>
+    <t>80 (244x122x2.5)</t>
   </si>
 </sst>
 </file>
@@ -177,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -187,6 +604,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -212,8 +653,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,7 +1064,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B7">
@@ -1068,4 +1524,1231 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1BAC92-B706-4ADC-AE6C-28D0DABEB4BB}">
+  <dimension ref="A1:H108"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7">
+        <v>2.7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" t="s">
+        <v>172</v>
+      </c>
+      <c r="G18">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="G30">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G40">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41">
+        <v>115</v>
+      </c>
+      <c r="H41" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G49">
+        <v>175</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G52">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G53">
+        <v>490</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="G54">
+        <v>40</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G55">
+        <v>270</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G60" t="s">
+        <v>152</v>
+      </c>
+      <c r="H60" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61">
+        <v>100</v>
+      </c>
+      <c r="G61" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G63" t="s">
+        <v>148</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G64" t="s">
+        <v>150</v>
+      </c>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="9"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B67" t="s">
+        <v>172</v>
+      </c>
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" t="s">
+        <v>172</v>
+      </c>
+      <c r="E67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F67" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B68" t="s">
+        <v>172</v>
+      </c>
+      <c r="C68" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" t="s">
+        <v>172</v>
+      </c>
+      <c r="E68" t="s">
+        <v>172</v>
+      </c>
+      <c r="F68" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C70" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" t="s">
+        <v>172</v>
+      </c>
+      <c r="E70" t="s">
+        <v>172</v>
+      </c>
+      <c r="F70" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="9"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="9"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="9"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="9"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B95" t="s">
+        <v>172</v>
+      </c>
+      <c r="C95" t="s">
+        <v>172</v>
+      </c>
+      <c r="D95" t="s">
+        <v>172</v>
+      </c>
+      <c r="E95" t="s">
+        <v>172</v>
+      </c>
+      <c r="F95" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B99" t="s">
+        <v>172</v>
+      </c>
+      <c r="C99" t="s">
+        <v>172</v>
+      </c>
+      <c r="D99" t="s">
+        <v>172</v>
+      </c>
+      <c r="E99" t="s">
+        <v>172</v>
+      </c>
+      <c r="F99" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G100">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G108">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H63:H64"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7406A2-D9F8-4EAB-B92F-23812B535E1F}">
+  <dimension ref="G43:G95"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="63" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G43" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G44" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G45" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G46" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G47" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G48" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G49" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G51" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G52" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G53" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G54" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G55" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G56" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G57" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G59" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G60" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G61" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="62" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G62" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G63" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G64" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G65" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G67" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G68" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G69" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G71" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G72" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G73" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G76" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G77" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G78" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G79" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G81" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G82" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G83" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G85" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G86" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G87" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G88" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G89" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G90" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G91" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G93" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G95" s="12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PROYECTOS/MEZANINE MA/Lista de materiales.xlsx
+++ b/PROYECTOS/MEZANINE MA/Lista de materiales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIC\Downloads\CURSO SKETCHUP\PROYECTOS\MEZANINE MA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D808547B-6AD1-478E-84E3-4A48EC1CA670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3489AF33-2659-4FD6-BC2F-B87FE8F0B7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9C38CAA7-9F0A-40CC-8992-24B3D9ED1EBA}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="184">
   <si>
     <t>LISTA DE MATERIALES</t>
   </si>
@@ -243,10 +243,6 @@
 62130000 Ventas</t>
   </si>
   <si>
-    <t>721 (Texturizado)
-793 (Synchro)</t>
-  </si>
-  <si>
     <t>590 (260x183)
 560 (260x183) Blanco Bernek</t>
   </si>
@@ -472,9 +468,6 @@
   </si>
   <si>
     <t>1 Alicate tapa tornillo 8mm (compatible para 3.5 y 4 mm)</t>
-  </si>
-  <si>
-    <t>1 Avellanador con tope</t>
   </si>
   <si>
     <t>30 (10 brocas)</t>
@@ -571,6 +564,38 @@
   </si>
   <si>
     <t>80 (244x122x2.5)</t>
+  </si>
+  <si>
+    <t>Synergy
+69252501 Ventas (Hugo Maydana)</t>
+  </si>
+  <si>
+    <t>667 (275x185x15)</t>
+  </si>
+  <si>
+    <t>793 (275x185x18)</t>
+  </si>
+  <si>
+    <t>721 (244x215) (Texturizado)
+793 (Synchro)</t>
+  </si>
+  <si>
+    <t>1 Nivel de burbuja (30 cm)</t>
+  </si>
+  <si>
+    <t>50 Soportes de repisa</t>
+  </si>
+  <si>
+    <t>1 broca para madera o metal de 3mm</t>
+  </si>
+  <si>
+    <t>1 bernier o calibrador</t>
+  </si>
+  <si>
+    <t>1 caution + pomada + estaño</t>
+  </si>
+  <si>
+    <t>1 Avellanador con tope de 8mm</t>
   </si>
 </sst>
 </file>
@@ -621,13 +646,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1528,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1BAC92-B706-4ADC-AE6C-28D0DABEB4BB}">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
@@ -1536,12 +1561,12 @@
     <col min="3" max="3" width="24.140625" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>47</v>
       </c>
@@ -1558,20 +1583,25 @@
         <v>53</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
       <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1579,19 +1609,22 @@
         <v>55</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="F3">
         <v>610</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -1599,29 +1632,32 @@
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="G4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" t="s">
         <v>173</v>
       </c>
-      <c r="B6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1634,11 +1670,17 @@
       <c r="D7">
         <v>2.7</v>
       </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
       <c r="F7" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -1649,7 +1691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -1657,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -1665,7 +1707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -1673,7 +1715,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1686,8 +1728,9 @@
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -1706,8 +1749,9 @@
       <c r="F13" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>42</v>
       </c>
@@ -1716,789 +1760,817 @@
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
       <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="10"/>
       <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" t="s">
-        <v>172</v>
-      </c>
-      <c r="F18" t="s">
-        <v>172</v>
-      </c>
-      <c r="G18">
+      <c r="B20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30">
         <v>80</v>
       </c>
-      <c r="H18" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H39">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H41">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" t="s">
+        <v>170</v>
+      </c>
+      <c r="D42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>164</v>
+      </c>
+      <c r="H43">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H44">
+        <v>115</v>
+      </c>
+      <c r="I44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="G19">
+      <c r="B45" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" t="s">
+        <v>170</v>
+      </c>
+      <c r="F45" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="H52">
+        <v>175</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>154</v>
+      </c>
+      <c r="H56">
+        <v>490</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57">
+        <v>40</v>
+      </c>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H58">
+        <v>270</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s">
+        <v>150</v>
+      </c>
+      <c r="I63" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64">
+        <v>100</v>
+      </c>
+      <c r="H64" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="H66" t="s">
+        <v>146</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="H67" t="s">
+        <v>148</v>
+      </c>
+      <c r="I67" s="13"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B70" t="s">
+        <v>170</v>
+      </c>
+      <c r="C70" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" t="s">
+        <v>170</v>
+      </c>
+      <c r="E70" t="s">
+        <v>170</v>
+      </c>
+      <c r="F70" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B71" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" t="s">
+        <v>170</v>
+      </c>
+      <c r="D71" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" t="s">
+        <v>170</v>
+      </c>
+      <c r="F71" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" t="s">
+        <v>170</v>
+      </c>
+      <c r="D73" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" t="s">
+        <v>170</v>
+      </c>
+      <c r="F73" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D20" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" t="s">
-        <v>172</v>
-      </c>
-      <c r="F20" t="s">
-        <v>172</v>
-      </c>
-      <c r="G20" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" t="s">
-        <v>172</v>
-      </c>
-      <c r="C23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" t="s">
-        <v>172</v>
-      </c>
-      <c r="G23">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G24">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" t="s">
-        <v>172</v>
-      </c>
-      <c r="F26" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" t="s">
-        <v>172</v>
-      </c>
-      <c r="F27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" t="s">
-        <v>172</v>
-      </c>
-      <c r="F28" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="G30">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" t="s">
-        <v>172</v>
-      </c>
-      <c r="C33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33" t="s">
-        <v>172</v>
-      </c>
-      <c r="E33" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="G36">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="G38">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B39" t="s">
-        <v>172</v>
-      </c>
-      <c r="C39" t="s">
-        <v>172</v>
-      </c>
-      <c r="D39" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="G40">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G41">
-        <v>115</v>
-      </c>
-      <c r="H41" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" t="s">
-        <v>172</v>
-      </c>
-      <c r="C42" t="s">
-        <v>172</v>
-      </c>
-      <c r="D42" t="s">
-        <v>172</v>
-      </c>
-      <c r="E42" t="s">
-        <v>172</v>
-      </c>
-      <c r="F42" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49">
-        <v>175</v>
-      </c>
-      <c r="H49" s="4" t="s">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B98" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" t="s">
+        <v>170</v>
+      </c>
+      <c r="D98" t="s">
+        <v>170</v>
+      </c>
+      <c r="E98" t="s">
+        <v>170</v>
+      </c>
+      <c r="F98" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" t="s">
+        <v>170</v>
+      </c>
+      <c r="D102" t="s">
+        <v>170</v>
+      </c>
+      <c r="E102" t="s">
+        <v>170</v>
+      </c>
+      <c r="F102" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H103">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="11" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="G52">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="G53">
-        <v>490</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>162</v>
-      </c>
-      <c r="G54">
-        <v>40</v>
-      </c>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="G55">
-        <v>270</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s">
-        <v>152</v>
-      </c>
-      <c r="H60" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61">
-        <v>100</v>
-      </c>
-      <c r="G61" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="G63" t="s">
-        <v>148</v>
-      </c>
-      <c r="H63" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G64" t="s">
-        <v>150</v>
-      </c>
-      <c r="H64" s="13"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="9"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B67" t="s">
-        <v>172</v>
-      </c>
-      <c r="C67" t="s">
-        <v>172</v>
-      </c>
-      <c r="D67" t="s">
-        <v>172</v>
-      </c>
-      <c r="E67" t="s">
-        <v>172</v>
-      </c>
-      <c r="F67" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B68" t="s">
-        <v>172</v>
-      </c>
-      <c r="C68" t="s">
-        <v>172</v>
-      </c>
-      <c r="D68" t="s">
-        <v>172</v>
-      </c>
-      <c r="E68" t="s">
-        <v>172</v>
-      </c>
-      <c r="F68" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" t="s">
-        <v>172</v>
-      </c>
-      <c r="C70" t="s">
-        <v>172</v>
-      </c>
-      <c r="D70" t="s">
-        <v>172</v>
-      </c>
-      <c r="E70" t="s">
-        <v>172</v>
-      </c>
-      <c r="F70" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="9"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="9"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="9"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="9"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B95" t="s">
-        <v>172</v>
-      </c>
-      <c r="C95" t="s">
-        <v>172</v>
-      </c>
-      <c r="D95" t="s">
-        <v>172</v>
-      </c>
-      <c r="E95" t="s">
-        <v>172</v>
-      </c>
-      <c r="F95" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B99" t="s">
-        <v>172</v>
-      </c>
-      <c r="C99" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" t="s">
-        <v>172</v>
-      </c>
-      <c r="E99" t="s">
-        <v>172</v>
-      </c>
-      <c r="F99" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="G100">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G108">
+      <c r="H111">
         <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="I66:I67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -2515,237 +2587,237 @@
   <sheetData>
     <row r="43" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G43" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G44" s="12" t="s">
-        <v>165</v>
+      <c r="G44" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G45" s="12" t="s">
-        <v>93</v>
+      <c r="G45" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G47" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G47" s="12" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="48" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G48" s="12" t="s">
-        <v>98</v>
+      <c r="G48" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G49" s="12" t="s">
-        <v>171</v>
+      <c r="G49" s="11" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G51" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G53" s="11" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G53" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
     <row r="54" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G54" s="12" t="s">
-        <v>160</v>
+      <c r="G54" s="11" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G55" s="12" t="s">
-        <v>90</v>
+      <c r="G55" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G56" s="12" t="s">
-        <v>166</v>
+      <c r="G56" s="11" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G57" s="12" t="s">
-        <v>143</v>
+      <c r="G57" s="11" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G59" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G60" s="12" t="s">
-        <v>103</v>
+      <c r="G60" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G61" s="12" t="s">
-        <v>158</v>
+      <c r="G61" s="11" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G62" s="12" t="s">
-        <v>107</v>
+      <c r="G62" s="11" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G64" s="11" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G64" s="12" t="s">
-        <v>156</v>
-      </c>
-    </row>
     <row r="65" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G65" s="12" t="s">
-        <v>163</v>
+      <c r="G65" s="11" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G67" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G68" s="12" t="s">
+      <c r="G68" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G69" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G71" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G69" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G70" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G71" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
     <row r="72" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G73" s="11" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G73" s="12" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G75" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G76" s="12" t="s">
+      <c r="G76" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G77" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G77" s="12" t="s">
+    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G78" s="11" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G78" s="12" t="s">
+    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G79" s="11" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G79" s="12" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="81" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G81" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G82" s="12" t="s">
-        <v>121</v>
+      <c r="G82" s="11" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G83" s="12" t="s">
-        <v>123</v>
+      <c r="G83" s="11" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G85" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G86" s="12" t="s">
+      <c r="G86" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G87" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G87" s="12" t="s">
+    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G88" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G88" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
     <row r="89" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G89" s="12" t="s">
+      <c r="G89" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G90" s="11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G90" s="12" t="s">
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G91" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G91" s="12" t="s">
+    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G92" s="12" t="s">
+    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G93" s="11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G93" s="12" t="s">
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G94" s="12" t="s">
-        <v>135</v>
-      </c>
-    </row>
     <row r="95" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G95" s="12" t="s">
-        <v>161</v>
+      <c r="G95" s="11" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
